--- a/data.mn/public/datasets/nso-foreign-trade-monthly.xlsx
+++ b/data.mn/public/datasets/nso-foreign-trade-monthly.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -427,106 +415,140 @@
   </sheetPr>
   <dimension ref="A1:AF49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
+    <col width="13" customWidth="1" min="20" max="20"/>
+    <col width="13" customWidth="1" min="21" max="21"/>
+    <col width="13" customWidth="1" min="22" max="22"/>
+    <col width="13" customWidth="1" min="23" max="23"/>
+    <col width="13" customWidth="1" min="24" max="24"/>
+    <col width="13" customWidth="1" min="25" max="25"/>
+    <col width="13" customWidth="1" min="26" max="26"/>
+    <col width="13" customWidth="1" min="27" max="27"/>
+    <col width="13" customWidth="1" min="28" max="28"/>
+    <col width="13" customWidth="1" min="29" max="29"/>
+    <col width="13" customWidth="1" min="30" max="30"/>
+    <col width="13" customWidth="1" min="31" max="31"/>
+    <col width="13" customWidth="1" min="32" max="32"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Indicator</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Month</t>
         </is>
       </c>
-      <c r="C1" s="1" t="n">
+      <c r="C1" t="n">
         <v>1997</v>
       </c>
-      <c r="D1" s="1" t="n">
+      <c r="D1" t="n">
         <v>1998</v>
       </c>
-      <c r="E1" s="1" t="n">
+      <c r="E1" t="n">
         <v>1999</v>
       </c>
-      <c r="F1" s="1" t="n">
+      <c r="F1" t="n">
         <v>2000</v>
       </c>
-      <c r="G1" s="1" t="n">
+      <c r="G1" t="n">
         <v>2001</v>
       </c>
-      <c r="H1" s="1" t="n">
+      <c r="H1" t="n">
         <v>2002</v>
       </c>
-      <c r="I1" s="1" t="n">
+      <c r="I1" t="n">
         <v>2003</v>
       </c>
-      <c r="J1" s="1" t="n">
+      <c r="J1" t="n">
         <v>2004</v>
       </c>
-      <c r="K1" s="1" t="n">
+      <c r="K1" t="n">
         <v>2005</v>
       </c>
-      <c r="L1" s="1" t="n">
+      <c r="L1" t="n">
         <v>2006</v>
       </c>
-      <c r="M1" s="1" t="n">
+      <c r="M1" t="n">
         <v>2007</v>
       </c>
-      <c r="N1" s="1" t="n">
+      <c r="N1" t="n">
         <v>2008</v>
       </c>
-      <c r="O1" s="1" t="n">
+      <c r="O1" t="n">
         <v>2009</v>
       </c>
-      <c r="P1" s="1" t="n">
+      <c r="P1" t="n">
         <v>2010</v>
       </c>
-      <c r="Q1" s="1" t="n">
+      <c r="Q1" t="n">
         <v>2011</v>
       </c>
-      <c r="R1" s="1" t="n">
+      <c r="R1" t="n">
         <v>2012</v>
       </c>
-      <c r="S1" s="1" t="n">
+      <c r="S1" t="n">
         <v>2013</v>
       </c>
-      <c r="T1" s="1" t="n">
+      <c r="T1" t="n">
         <v>2014</v>
       </c>
-      <c r="U1" s="1" t="n">
+      <c r="U1" t="n">
         <v>2015</v>
       </c>
-      <c r="V1" s="1" t="n">
+      <c r="V1" t="n">
         <v>2016</v>
       </c>
-      <c r="W1" s="1" t="n">
+      <c r="W1" t="n">
         <v>2017</v>
       </c>
-      <c r="X1" s="1" t="n">
+      <c r="X1" t="n">
         <v>2018</v>
       </c>
-      <c r="Y1" s="1" t="n">
+      <c r="Y1" t="n">
         <v>2019</v>
       </c>
-      <c r="Z1" s="1" t="n">
+      <c r="Z1" t="n">
         <v>2020</v>
       </c>
-      <c r="AA1" s="1" t="n">
+      <c r="AA1" t="n">
         <v>2021</v>
       </c>
-      <c r="AB1" s="1" t="n">
+      <c r="AB1" t="n">
         <v>2022</v>
       </c>
-      <c r="AC1" s="1" t="n">
+      <c r="AC1" t="n">
         <v>2023</v>
       </c>
-      <c r="AD1" s="1" t="n">
+      <c r="AD1" t="n">
         <v>2024</v>
       </c>
-      <c r="AE1" s="1" t="n">
+      <c r="AE1" t="n">
         <v>2025</v>
       </c>
-      <c r="AF1" s="1" t="n">
+      <c r="AF1" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -731,7 +753,7 @@
         <v>246.89</v>
       </c>
       <c r="AF3" t="n">
-        <v>553.09</v>
+        <v>553.0700000000001</v>
       </c>
     </row>
     <row r="4">
@@ -833,7 +855,7 @@
         <v>173.99</v>
       </c>
       <c r="AF4" t="n">
-        <v>938.5700000000001</v>
+        <v>939.52</v>
       </c>
     </row>
     <row r="5">
@@ -935,7 +957,7 @@
         <v>218.45</v>
       </c>
       <c r="AF5" t="n">
-        <v>735.25</v>
+        <v>735.39</v>
       </c>
     </row>
     <row r="6">
@@ -1036,7 +1058,9 @@
       <c r="AE6" t="n">
         <v>175.1</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
+      <c r="AF6" t="n">
+        <v>447.72</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1136,7 +1160,9 @@
       <c r="AE7" t="n">
         <v>191.92</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
+      <c r="AF7" t="n">
+        <v>687.65</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1236,7 +1262,9 @@
       <c r="AE8" t="n">
         <v>217.08</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
+      <c r="AF8" t="n">
+        <v>766.97</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2143,7 +2171,7 @@
         <v>1229.57</v>
       </c>
       <c r="AF17" t="n">
-        <v>1923.78</v>
+        <v>1923.81</v>
       </c>
     </row>
     <row r="18">
@@ -2244,7 +2272,9 @@
       <c r="AE18" t="n">
         <v>1156.08</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
+      <c r="AF18" t="n">
+        <v>1657.46</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2344,7 +2374,9 @@
       <c r="AE19" t="n">
         <v>1182.98</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
+      <c r="AF19" t="n">
+        <v>1923.38</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2444,7 +2476,9 @@
       <c r="AE20" t="n">
         <v>1170.88</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
+      <c r="AF20" t="n">
+        <v>1812.04</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3147,7 +3181,7 @@
         <v>738.5</v>
       </c>
       <c r="AF27" t="n">
-        <v>732.78</v>
+        <v>732.8099999999999</v>
       </c>
     </row>
     <row r="28">
@@ -3249,7 +3283,7 @@
         <v>834.05</v>
       </c>
       <c r="AF28" t="n">
-        <v>904.26</v>
+        <v>903.3099999999999</v>
       </c>
     </row>
     <row r="29">
@@ -3351,7 +3385,7 @@
         <v>1011.12</v>
       </c>
       <c r="AF29" t="n">
-        <v>1188.53</v>
+        <v>1188.42</v>
       </c>
     </row>
     <row r="30">
@@ -3452,7 +3486,9 @@
       <c r="AE30" t="n">
         <v>980.98</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
+      <c r="AF30" t="n">
+        <v>1209.74</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3552,7 +3588,9 @@
       <c r="AE31" t="n">
         <v>991.05</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
+      <c r="AF31" t="n">
+        <v>1235.73</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3652,7 +3690,9 @@
       <c r="AE32" t="n">
         <v>953.8</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
+      <c r="AF32" t="n">
+        <v>1045.07</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -4355,7 +4395,7 @@
         <v>1723.88</v>
       </c>
       <c r="AF39" t="n">
-        <v>2018.65</v>
+        <v>2018.68</v>
       </c>
     </row>
     <row r="40">
@@ -4457,7 +4497,7 @@
         <v>1842.09</v>
       </c>
       <c r="AF40" t="n">
-        <v>2747.1</v>
+        <v>2746.14</v>
       </c>
     </row>
     <row r="41">
@@ -4559,7 +4599,7 @@
         <v>2240.69</v>
       </c>
       <c r="AF41" t="n">
-        <v>3112.31</v>
+        <v>3112.23</v>
       </c>
     </row>
     <row r="42">
@@ -4660,7 +4700,9 @@
       <c r="AE42" t="n">
         <v>2137.05</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
+      <c r="AF42" t="n">
+        <v>2867.21</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -4760,7 +4802,9 @@
       <c r="AE43" t="n">
         <v>2174.03</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
+      <c r="AF43" t="n">
+        <v>3159.12</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4860,7 +4904,9 @@
       <c r="AE44" t="n">
         <v>2124.67</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
+      <c r="AF44" t="n">
+        <v>2857.11</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
